--- a/AAII_Financials/Yearly/NECPY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NECPY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
   <si>
     <t>NECPY</t>
   </si>
@@ -656,135 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22532200</v>
+      </c>
+      <c r="E8" s="3">
         <v>22861300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22989400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24922300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24820800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>27071000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>28765600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>26292300</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>15102900</v>
+      </c>
+      <c r="E9" s="3">
         <v>15779000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16339300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17713800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17521300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>19284400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20517000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18802600</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7429300</v>
+      </c>
+      <c r="E10" s="3">
         <v>7082300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6650100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7208400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7299500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7786500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8248500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7489700</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -796,35 +808,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>661900</v>
+      </c>
+      <c r="E12" s="3">
         <v>662400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>765500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>912900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1039800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1073400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1058600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1012700</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -849,63 +865,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
+      <c r="D14" s="3">
+        <v>-114500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="3">
         <v>28100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-80200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-250000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>28400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>192000</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>971700</v>
+      </c>
+      <c r="E15" s="3">
         <v>1058000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1241000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1378900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1486700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>546100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>565800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>475300</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -914,62 +939,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20268700</v>
+      </c>
+      <c r="E17" s="3">
         <v>21148400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21746400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23640100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23729500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25900300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27550000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25465100</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2263500</v>
+      </c>
+      <c r="E18" s="3">
         <v>1712900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1243000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1282200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1091300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1170700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1215600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>827200</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -981,143 +1013,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-126700</v>
+      </c>
+      <c r="E20" s="3">
         <v>112900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-14900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-36200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-36500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>10000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-57400</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3361900</v>
+      </c>
+      <c r="E21" s="3">
         <v>2658000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2485500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2675900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2614300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1753200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1771400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1359900</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>60100</v>
+      </c>
+      <c r="E22" s="3">
         <v>63200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>80300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>60200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>66100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>77100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>91500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>62000</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2504200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1601200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1223200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1261300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1189400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1427100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1152100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>697700</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>785200</v>
+      </c>
+      <c r="E24" s="3">
         <v>368000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>133900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>272000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-101000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-36500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>104600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>229000</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1142,63 +1190,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1719000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1233200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1089200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>989300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1290400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1463500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1047600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>468600</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1699500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1169800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>988500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>861300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1163400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1352700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>929000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>358100</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1223,9 +1280,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1250,9 +1310,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1277,9 +1340,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1304,63 +1370,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>126700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-112900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>14900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>36200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>36500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-10000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>57400</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1699500</v>
+      </c>
+      <c r="E33" s="3">
         <v>1169900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>988500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>861300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1163400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1352700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>929000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>358000</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1385,68 +1460,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1699500</v>
+      </c>
+      <c r="E35" s="3">
         <v>1169900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>988500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>861300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1163400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1352700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>929000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>358000</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1458,8 +1542,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1471,35 +1556,39 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4144700</v>
+      </c>
+      <c r="E41" s="3">
         <v>3904000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3150200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3155400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3547400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4731900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3338700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2511600</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1516,206 +1605,230 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>86600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>51900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>53000</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6251800</v>
+      </c>
+      <c r="E43" s="3">
         <v>5866100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5484100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6017100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5948400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9139100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9155100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9121600</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1076600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1233900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1604100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2012800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2027800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1677700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1852400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2117300</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3555200</v>
+      </c>
+      <c r="E45" s="3">
         <v>3329900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3467600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3328100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3110200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>647800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>975600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>585800</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15465500</v>
+      </c>
+      <c r="E46" s="3">
         <v>14858300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14160100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15014200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15125000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16825000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15788900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14784200</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2751600</v>
+      </c>
+      <c r="E47" s="3">
         <v>3921300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4322600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3994500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4288700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2565500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2726900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2913400</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3547500</v>
+      </c>
+      <c r="E48" s="3">
         <v>3874300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3378200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4238100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4449000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5001600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5186500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3689400</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5153600</v>
+      </c>
+      <c r="E49" s="3">
         <v>4980300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5051400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5520200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5852400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5886100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3348600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3441700</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1740,9 +1853,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1767,9 +1883,12 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1785,18 +1904,21 @@
       <c r="G52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I52" s="3">
         <v>1514900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>243800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>325400</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1821,36 +1943,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>28092100</v>
+      </c>
+      <c r="E54" s="3">
         <v>28817500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27949600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>29970100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30977600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33170000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29026000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>26741500</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1862,8 +1990,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1875,170 +2004,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2996800</v>
+      </c>
+      <c r="E57" s="3">
         <v>3291100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3436300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3743400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3679300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3790700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3751500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3716300</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>669000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1912600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>907400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1338400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1945400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>895000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1878000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1432000</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4566400</v>
+      </c>
+      <c r="E59" s="3">
         <v>3991100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3699900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3378300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3448000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4189100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3946700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3689400</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9836000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10864200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9714400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10272100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10985300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10827600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11355400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10452200</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2407700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2537300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2719900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3238900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2974000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5460000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4399000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3502600</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>497800</v>
+      </c>
+      <c r="E62" s="3">
         <v>447300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>412900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>387600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>457800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>607100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>608900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>807000</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2063,9 +2211,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2090,9 +2241,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2117,36 +2271,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13741100</v>
+      </c>
+      <c r="E66" s="3">
         <v>14984200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14135000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15581600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16264700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19048400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18668200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17178400</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2158,8 +2318,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2184,9 +2345,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2211,9 +2375,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2238,9 +2405,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2265,36 +2435,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7649600</v>
+      </c>
+      <c r="E72" s="3">
         <v>6837800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5840800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5751800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5588700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5105500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4055300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3199900</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2319,9 +2495,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2346,9 +2525,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2373,36 +2555,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13814500</v>
+      </c>
+      <c r="E76" s="3">
         <v>13035400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12664800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12215200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12463600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11827900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8463400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7751500</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2427,68 +2615,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1699500</v>
+      </c>
+      <c r="E81" s="3">
         <v>1169900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>988500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>861300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1163400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1352700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>929000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>358000</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2500,35 +2697,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>971700</v>
+      </c>
+      <c r="E83" s="3">
         <v>1058000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1241000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1378900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1486700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>897200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>936100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>410500</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2553,9 +2754,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2580,9 +2784,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2607,9 +2814,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2634,9 +2844,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2661,36 +2874,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2757500</v>
+      </c>
+      <c r="E89" s="3">
         <v>2299900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1793200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1144400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1214800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2485600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2433600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>579700</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2702,35 +2921,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-442300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-844200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-497000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-424200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-469000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-536200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-676800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-441600</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2755,9 +2978,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2782,36 +3008,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>211900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-875900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-502600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-373000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-521900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1107500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-780900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-692000</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2823,35 +3055,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>251800</v>
+      </c>
+      <c r="E96" s="3">
         <v>231600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>202700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>214600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>224500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>192600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>168900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>140700</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2876,9 +3112,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2903,9 +3142,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2930,88 +3172,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2628500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-694300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1028100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-923700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1561500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-852700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-455800</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>127200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>114500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>67200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>106300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>55400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-41800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11500</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>468000</v>
+      </c>
+      <c r="E102" s="3">
         <v>722000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>377000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-85100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-762300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1446100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>758300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-579500</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
